--- a/upload/cirurgia_2019.xlsx
+++ b/upload/cirurgia_2019.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R6f5b920775e5470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rcc7da5f394e7469b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26034,22 +26034,2781 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>733</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>760</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1026</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c s="8">
         <x:v>241</x:v>
       </x:c>
       <x:c s="8">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1062</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>747</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>736</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>893</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c s="8">
         <x:v>71</x:v>
       </x:c>
       <x:c s="8">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>448</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>403</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>368</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>346</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -26059,2570 +28818,121 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>242</x:v>
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>394</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>252</x:v>
       </x:c>
       <x:c s="8">
         <x:v>76</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>358</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>356</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>325</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>239</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>270</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>370</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>310</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>356</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>346</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>387</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HAC</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>388</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HCM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>541</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>432</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>733</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>453</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>643</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>750</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>760</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>791</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJK</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>816</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>892</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>887</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>904</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>679</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1026</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>714</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1020</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>695</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1029</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>721</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1062</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HJXXIII</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>747</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>51</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c s="8">
         <x:v>20</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1082</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HMAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>882</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>736</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>875</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>718</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>893</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>406</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>930</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>240</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>428</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>441</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>260</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>270</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>301</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>268</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>340</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>319</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>325</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>342</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>355</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>374</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>448</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>449</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>433</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>403</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>428</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>424</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>342</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>390</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>437</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>368</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>420</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>385</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>394</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>415</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row/>
